--- a/produits/preuves/sortie/c7-momo/c7-momo.xlsx
+++ b/produits/preuves/sortie/c7-momo/c7-momo.xlsx
@@ -292,6 +292,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -371,6 +372,9 @@
   </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.87"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
